--- a/data/Kanaleneiland/archetypes/pop_archetypes_citizen.xlsx
+++ b/data/Kanaleneiland/archetypes/pop_archetypes_citizen.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asier.divasson\Documents\GitHub\CogniCity\data\Kanaleneiland\archetypes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asier.divasson\Documents\GitHub\CogniCity\data\s0\Kanaleneiland\archetypes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{801CF929-EC2F-44B9-90FD-D48BD17F04BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CDBA5E9-ED25-4BE5-B855-7F82535C9056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -742,10 +742,10 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="AE2">
-        <v>12764</v>
+        <v>5000</v>
       </c>
       <c r="AF2">
-        <v>587</v>
+        <v>250</v>
       </c>
       <c r="AG2">
         <v>14597</v>
@@ -846,10 +846,10 @@
         <v>7.1999999999999995E-2</v>
       </c>
       <c r="AE3">
-        <v>10415</v>
+        <v>5000</v>
       </c>
       <c r="AF3">
-        <v>636</v>
+        <v>250</v>
       </c>
       <c r="AG3">
         <v>10736</v>
@@ -950,10 +950,10 @@
         <v>4.2000000000000003E-2</v>
       </c>
       <c r="AE4">
-        <v>3822</v>
+        <v>5000</v>
       </c>
       <c r="AF4">
-        <v>402</v>
+        <v>250</v>
       </c>
       <c r="AG4">
         <v>6860</v>
@@ -1054,10 +1054,10 @@
         <v>6.7000000000000004E-2</v>
       </c>
       <c r="AE5">
-        <v>5900</v>
+        <v>5000</v>
       </c>
       <c r="AF5">
-        <v>1259</v>
+        <v>250</v>
       </c>
       <c r="AG5">
         <v>10735</v>
@@ -1158,10 +1158,10 @@
         <v>4.2000000000000003E-2</v>
       </c>
       <c r="AE6">
-        <v>12301</v>
+        <v>5000</v>
       </c>
       <c r="AF6">
-        <v>1298</v>
+        <v>250</v>
       </c>
       <c r="AG6">
         <v>13621</v>
